--- a/ROZVRH.xlsx
+++ b/ROZVRH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telcocloud-my.sharepoint.com/personal/michal_tonder_o2_sk/Documents/Desktop/PROJECT BIG JAPAN 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{E5188EBF-1E66-4EA4-831E-1393EE5B905B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBC43F72-5139-4FE3-A542-782B516019D6}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{E5188EBF-1E66-4EA4-831E-1393EE5B905B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861AE6FE-D250-4451-8564-3C7BD42D12FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1493,10 +1493,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="d\.m"/>
-    <numFmt numFmtId="166" formatCode="d\.m\."/>
-    <numFmt numFmtId="167" formatCode="#,##0&quot;€&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0&quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="d\.m"/>
+    <numFmt numFmtId="165" formatCode="d\.m\."/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;€&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0&quot;€&quot;"/>
   </numFmts>
   <fonts count="53" x14ac:knownFonts="1">
     <font>
@@ -2151,52 +2151,68 @@
     <xf numFmtId="0" fontId="46" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="23" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2204,82 +2220,66 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="9" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="23" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2510,7 +2510,7 @@
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
     <col min="6" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="73.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
     <col min="10" max="10" width="26.6640625" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" customWidth="1"/>
     <col min="12" max="13" width="8" customWidth="1"/>
@@ -2534,39 +2534,39 @@
       <c r="G1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="J1" s="80" t="s">
+      <c r="J1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="83" t="s">
+      <c r="L1" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="M1" s="83" t="s">
+      <c r="M1" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="83" t="s">
+      <c r="N1" s="41" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40">
+      <c r="A2" s="55">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="86">
+      <c r="C2" s="58">
         <v>46283</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="55">
         <v>1</v>
       </c>
       <c r="E2" s="6"/>
@@ -2574,43 +2574,43 @@
         <v>25</v>
       </c>
       <c r="G2" s="8"/>
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="41"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="41"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="49"/>
       <c r="E3" s="9"/>
       <c r="F3" s="10">
         <v>0.47569444444444442</v>
       </c>
       <c r="G3" s="9"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58" t="s">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="58">
         <v>46284</v>
       </c>
-      <c r="D4" s="57"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
@@ -2620,23 +2620,23 @@
       <c r="G4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="59" t="str">
+      <c r="H4" s="60" t="str">
         <f>G4</f>
         <v>KISHIDAWA</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="55">
+      <c r="L4" s="48">
         <v>46279</v>
       </c>
-      <c r="M4" s="56">
+      <c r="M4" s="50">
         <v>58</v>
       </c>
       <c r="N4" s="12" t="s">
@@ -2644,10 +2644,10 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="41"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="10">
         <v>0.22916666666666666</v>
       </c>
@@ -2655,25 +2655,25 @@
         <v>43</v>
       </c>
       <c r="G5" s="14"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="45"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
       <c r="N5" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58" t="s">
+      <c r="A6" s="63"/>
+      <c r="B6" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="58">
         <v>46285</v>
       </c>
-      <c r="D6" s="57"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="11" t="s">
         <v>3</v>
       </c>
@@ -2683,23 +2683,23 @@
       <c r="G6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="59" t="str">
+      <c r="H6" s="60" t="str">
         <f>G6</f>
         <v>OSAKA</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="60" t="s">
+      <c r="J6" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="48" t="s">
+      <c r="K6" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="48">
         <v>46283</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="50">
         <v>43</v>
       </c>
       <c r="N6" s="17" t="s">
@@ -2707,34 +2707,34 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="41"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="49"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="45"/>
       <c r="I7" s="18"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="18" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="61">
+      <c r="A8" s="69">
         <v>0</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="58">
         <v>46286</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="69">
         <v>0</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -2746,56 +2746,56 @@
       <c r="G8" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="59" t="str">
+      <c r="H8" s="60" t="str">
         <f>G8</f>
         <v>OSAKA</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="60" t="s">
+      <c r="J8" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="48" t="s">
+      <c r="K8" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="55">
+      <c r="L8" s="48">
         <v>46283</v>
       </c>
-      <c r="M8" s="56">
+      <c r="M8" s="50">
         <v>43</v>
       </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="41"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="49"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="53"/>
+      <c r="H9" s="45"/>
       <c r="I9" s="20"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
       <c r="N9" s="20"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="61">
+      <c r="A10" s="69">
         <v>0</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="86">
+      <c r="C10" s="58">
         <v>46287</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="69">
         <v>0</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -2807,56 +2807,56 @@
       <c r="G10" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="59" t="str">
+      <c r="H10" s="60" t="str">
         <f>G10</f>
         <v>OSAKA</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="48" t="s">
+      <c r="K10" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="L10" s="55">
+      <c r="L10" s="48">
         <v>46283</v>
       </c>
-      <c r="M10" s="56">
+      <c r="M10" s="50">
         <v>43</v>
       </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="41"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="49"/>
       <c r="E11" s="21"/>
       <c r="F11" s="9"/>
       <c r="G11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="53"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="20"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
       <c r="N11" s="20"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="61">
+      <c r="A12" s="69">
         <v>0</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="58">
         <v>46288</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="69">
         <v>0</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -2868,32 +2868,32 @@
       <c r="G12" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="59" t="str">
+      <c r="H12" s="60" t="str">
         <f>G12</f>
         <v>OSAKA</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="60" t="s">
+      <c r="J12" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="48" t="s">
+      <c r="K12" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="55">
+      <c r="L12" s="48">
         <v>46283</v>
       </c>
-      <c r="M12" s="56">
+      <c r="M12" s="50">
         <v>43</v>
       </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="41"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
         <v>58</v>
@@ -2901,25 +2901,25 @@
       <c r="G13" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="53"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="20"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
       <c r="N13" s="20"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="61">
+      <c r="A14" s="69">
         <v>0</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="58">
         <v>46289</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="69">
         <v>0</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -2931,54 +2931,54 @@
       <c r="G14" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="59" t="str">
+      <c r="H14" s="60" t="str">
         <f>G14</f>
         <v>OSAKA</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="60" t="s">
+      <c r="J14" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="48" t="s">
+      <c r="K14" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="55">
+      <c r="L14" s="48">
         <v>46283</v>
       </c>
-      <c r="M14" s="56">
+      <c r="M14" s="50">
         <v>43</v>
       </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="41"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="49"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="22"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="20"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
       <c r="N15" s="20"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="40">
+      <c r="A16" s="55">
         <v>1</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="58">
         <v>46290</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="55">
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -2990,54 +2990,54 @@
       <c r="G16" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="59" t="str">
+      <c r="H16" s="60" t="str">
         <f>G16</f>
         <v>OSAKA</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="60" t="s">
+      <c r="J16" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K16" s="48" t="s">
+      <c r="K16" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="L16" s="55">
+      <c r="L16" s="48">
         <v>46283</v>
       </c>
-      <c r="M16" s="56">
+      <c r="M16" s="50">
         <v>43</v>
       </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="41"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="49"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="53"/>
+      <c r="H17" s="45"/>
       <c r="I17" s="20"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
       <c r="N17" s="20"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58" t="s">
+      <c r="A18" s="63"/>
+      <c r="B18" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="58">
         <v>46291</v>
       </c>
-      <c r="D18" s="57"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="11" t="s">
         <v>3</v>
       </c>
@@ -3047,54 +3047,54 @@
       <c r="G18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="59" t="str">
+      <c r="H18" s="60" t="str">
         <f>G18</f>
         <v>OSAKA</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="60" t="s">
+      <c r="J18" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="K18" s="48" t="s">
+      <c r="K18" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="48">
         <v>46283</v>
       </c>
-      <c r="M18" s="56">
+      <c r="M18" s="50">
         <v>43</v>
       </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="41"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="41"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="49"/>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
       <c r="G19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="53"/>
+      <c r="H19" s="45"/>
       <c r="I19" s="20"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
       <c r="N19" s="20"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="57"/>
-      <c r="B20" s="58" t="s">
+      <c r="A20" s="63"/>
+      <c r="B20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="58">
         <v>46292</v>
       </c>
-      <c r="D20" s="57"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="11" t="s">
         <v>3</v>
       </c>
@@ -3104,23 +3104,23 @@
       <c r="G20" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="59" t="str">
+      <c r="H20" s="60" t="str">
         <f>G20</f>
         <v>KYOTO</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="J20" s="54" t="s">
+      <c r="J20" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="48" t="s">
+      <c r="K20" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="L20" s="55">
+      <c r="L20" s="48">
         <v>46291</v>
       </c>
-      <c r="M20" s="56">
+      <c r="M20" s="50">
         <v>24</v>
       </c>
       <c r="N20" s="17" t="s">
@@ -3128,32 +3128,32 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="41"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="49"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="45"/>
       <c r="I21" s="20"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
       <c r="N21" s="20"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40">
+      <c r="A22" s="55">
         <v>1</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="58">
         <v>46293</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="55">
         <v>1</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -3165,23 +3165,23 @@
       <c r="G22" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="59" t="str">
+      <c r="H22" s="60" t="str">
         <f>G22</f>
         <v>KYOTO</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="54" t="s">
+      <c r="J22" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="K22" s="48" t="s">
+      <c r="K22" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="L22" s="55">
+      <c r="L22" s="48">
         <v>46291</v>
       </c>
-      <c r="M22" s="56">
+      <c r="M22" s="50">
         <v>24</v>
       </c>
       <c r="N22" s="17" t="s">
@@ -3189,34 +3189,34 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="41"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="41"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="49"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="22"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="45"/>
       <c r="I23" s="20"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
       <c r="N23" s="20"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="63">
+      <c r="A24" s="86">
         <v>0.5</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="86">
+      <c r="C24" s="58">
         <v>46294</v>
       </c>
-      <c r="D24" s="61">
+      <c r="D24" s="69">
         <v>0</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -3228,23 +3228,23 @@
       <c r="G24" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="59" t="str">
+      <c r="H24" s="60" t="str">
         <f>G24</f>
         <v>KYOTO</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="54" t="s">
+      <c r="J24" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="K24" s="48" t="s">
+      <c r="K24" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="48">
         <v>46291</v>
       </c>
-      <c r="M24" s="56">
+      <c r="M24" s="50">
         <v>24</v>
       </c>
       <c r="N24" s="17" t="s">
@@ -3252,10 +3252,10 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="41"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="49"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
         <v>73</v>
@@ -3263,25 +3263,25 @@
       <c r="G25" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="53"/>
+      <c r="H25" s="45"/>
       <c r="I25" s="20"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
       <c r="N25" s="20"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="61">
+      <c r="A26" s="69">
         <v>0</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="86">
+      <c r="C26" s="58">
         <v>46295</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="69">
         <v>0</v>
       </c>
       <c r="E26" s="11" t="s">
@@ -3293,23 +3293,23 @@
       <c r="G26" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="59" t="str">
+      <c r="H26" s="60" t="str">
         <f>G26</f>
         <v>KYOTO</v>
       </c>
       <c r="I26" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="J26" s="60" t="s">
+      <c r="J26" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="K26" s="48" t="s">
+      <c r="K26" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="L26" s="55">
+      <c r="L26" s="48">
         <v>46294</v>
       </c>
-      <c r="M26" s="56">
+      <c r="M26" s="50">
         <v>25</v>
       </c>
       <c r="N26" s="25" t="s">
@@ -3317,34 +3317,34 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="41"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="41"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="49"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="53"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="20"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
       <c r="N27" s="20"/>
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="62">
+      <c r="A28" s="79">
         <v>0</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="86">
+      <c r="C28" s="58">
         <v>46296</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="79">
         <v>0</v>
       </c>
       <c r="E28" s="11" t="s">
@@ -3356,23 +3356,23 @@
       <c r="G28" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H28" s="59" t="str">
+      <c r="H28" s="60" t="str">
         <f>G28</f>
         <v>OTSU</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="54" t="s">
+      <c r="J28" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="K28" s="49" t="s">
+      <c r="K28" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="L28" s="55">
+      <c r="L28" s="48">
         <v>46293</v>
       </c>
-      <c r="M28" s="56">
+      <c r="M28" s="50">
         <v>41</v>
       </c>
       <c r="N28" s="17" t="s">
@@ -3380,10 +3380,10 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="41"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="41"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="49"/>
       <c r="E29" s="9" t="s">
         <v>121</v>
       </c>
@@ -3393,25 +3393,25 @@
       <c r="G29" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="53"/>
+      <c r="H29" s="45"/>
       <c r="I29" s="20"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
       <c r="N29" s="20"/>
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="62">
+      <c r="A30" s="79">
         <v>0</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="86">
+      <c r="C30" s="58">
         <v>46297</v>
       </c>
-      <c r="D30" s="62">
+      <c r="D30" s="79">
         <v>0</v>
       </c>
       <c r="E30" s="11" t="s">
@@ -3423,23 +3423,23 @@
       <c r="G30" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H30" s="59" t="str">
+      <c r="H30" s="60" t="str">
         <f>G30</f>
         <v>HIKONE</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="J30" s="60" t="s">
+      <c r="J30" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="K30" s="45" t="s">
+      <c r="K30" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="L30" s="55">
+      <c r="L30" s="48">
         <v>46293</v>
       </c>
-      <c r="M30" s="56">
+      <c r="M30" s="50">
         <v>41</v>
       </c>
       <c r="N30" s="17" t="s">
@@ -3447,32 +3447,32 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="41"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="41"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="49"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="53"/>
+      <c r="H31" s="45"/>
       <c r="I31" s="20"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="49"/>
       <c r="N31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A32" s="57"/>
-      <c r="B32" s="58" t="s">
+      <c r="A32" s="63"/>
+      <c r="B32" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="86">
+      <c r="C32" s="58">
         <v>46298</v>
       </c>
-      <c r="D32" s="57"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="11" t="s">
         <v>85</v>
       </c>
@@ -3482,23 +3482,23 @@
       <c r="G32" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="59" t="str">
+      <c r="H32" s="60" t="str">
         <f>G32</f>
         <v>OSAKA</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="64" t="s">
+      <c r="J32" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="K32" s="45" t="s">
+      <c r="K32" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="L32" s="55">
+      <c r="L32" s="48">
         <v>46296</v>
       </c>
-      <c r="M32" s="56">
+      <c r="M32" s="50">
         <v>41</v>
       </c>
       <c r="N32" s="17" t="s">
@@ -3506,30 +3506,30 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A33" s="41"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="41"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="49"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
-      <c r="H33" s="53"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="20"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="38"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
       <c r="N33" s="20"/>
     </row>
     <row r="34" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="57"/>
-      <c r="B34" s="58" t="s">
+      <c r="A34" s="63"/>
+      <c r="B34" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="86">
+      <c r="C34" s="58">
         <v>46299</v>
       </c>
-      <c r="D34" s="57"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="11" t="s">
         <v>3</v>
       </c>
@@ -3539,23 +3539,23 @@
       <c r="G34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H34" s="59" t="str">
+      <c r="H34" s="60" t="str">
         <f>G34</f>
         <v>OSAKA</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="J34" s="64" t="s">
+      <c r="J34" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="K34" s="45" t="s">
+      <c r="K34" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="L34" s="55">
+      <c r="L34" s="48">
         <v>46296</v>
       </c>
-      <c r="M34" s="56">
+      <c r="M34" s="50">
         <v>41</v>
       </c>
       <c r="N34" s="27" t="s">
@@ -3563,34 +3563,34 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="41"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
         <v>92</v>
       </c>
       <c r="G35" s="14"/>
-      <c r="H35" s="53"/>
+      <c r="H35" s="45"/>
       <c r="I35" s="20"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="38"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
       <c r="N35" s="20"/>
     </row>
     <row r="36" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A36" s="61">
+      <c r="A36" s="69">
         <v>0</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="86">
+      <c r="C36" s="58">
         <v>46300</v>
       </c>
-      <c r="D36" s="61">
+      <c r="D36" s="69">
         <v>0</v>
       </c>
       <c r="E36" s="11" t="s">
@@ -3602,23 +3602,23 @@
       <c r="G36" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="59" t="str">
+      <c r="H36" s="60" t="str">
         <f>G36</f>
         <v>FUKUYAMA</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="J36" s="60" t="s">
+      <c r="J36" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="K36" s="45" t="s">
+      <c r="K36" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="L36" s="55">
+      <c r="L36" s="48">
         <v>46298</v>
       </c>
-      <c r="M36" s="56">
+      <c r="M36" s="50">
         <v>36</v>
       </c>
       <c r="N36" s="17" t="s">
@@ -3626,34 +3626,34 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="41"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="41"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="49"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="53"/>
+      <c r="H37" s="45"/>
       <c r="I37" s="20"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
       <c r="N37" s="20"/>
     </row>
     <row r="38" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A38" s="40">
+      <c r="A38" s="55">
         <v>1</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="58">
         <v>46301</v>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="55">
         <v>1</v>
       </c>
       <c r="E38" s="11" t="s">
@@ -3665,23 +3665,23 @@
       <c r="G38" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="H38" s="59" t="str">
+      <c r="H38" s="60" t="str">
         <f>G38</f>
         <v>OMISHIMA</v>
       </c>
       <c r="I38" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="J38" s="65" t="s">
+      <c r="J38" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="L38" s="55">
+      <c r="L38" s="48">
         <v>46299</v>
       </c>
-      <c r="M38" s="56">
+      <c r="M38" s="50">
         <v>25</v>
       </c>
       <c r="N38" s="17" t="s">
@@ -3689,10 +3689,10 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="41"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="49"/>
       <c r="E39" s="9" t="s">
         <v>99</v>
       </c>
@@ -3700,25 +3700,25 @@
         <v>100</v>
       </c>
       <c r="G39" s="22"/>
-      <c r="H39" s="53"/>
+      <c r="H39" s="45"/>
       <c r="I39" s="20"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="49"/>
       <c r="N39" s="20"/>
     </row>
     <row r="40" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A40" s="40">
+      <c r="A40" s="55">
         <v>1</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="86">
+      <c r="C40" s="58">
         <v>46302</v>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="55">
         <v>1</v>
       </c>
       <c r="E40" s="11"/>
@@ -3728,23 +3728,23 @@
       <c r="G40" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="59" t="str">
+      <c r="H40" s="60" t="str">
         <f>G40</f>
         <v>MASTUYAMA</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="J40" s="60" t="s">
+      <c r="J40" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="K40" s="46" t="s">
+      <c r="K40" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="L40" s="55">
+      <c r="L40" s="48">
         <v>46302</v>
       </c>
-      <c r="M40" s="76">
+      <c r="M40" s="65">
         <v>27</v>
       </c>
       <c r="N40" s="17" t="s">
@@ -3752,34 +3752,34 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="41"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="41"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="49"/>
       <c r="E41" s="9" t="s">
         <v>104</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="22"/>
-      <c r="H41" s="53"/>
+      <c r="H41" s="45"/>
       <c r="I41" s="20"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="47"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
       <c r="N41" s="20"/>
     </row>
     <row r="42" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A42" s="40">
+      <c r="A42" s="55">
         <v>1</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="86">
+      <c r="C42" s="58">
         <v>46303</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="55">
         <v>1</v>
       </c>
       <c r="E42" s="11" t="s">
@@ -3791,54 +3791,54 @@
       <c r="G42" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="59" t="str">
+      <c r="H42" s="60" t="str">
         <f>G42</f>
         <v>BEPPU</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="J42" s="54" t="s">
+      <c r="J42" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="K42" s="45" t="s">
+      <c r="K42" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="L42" s="77" t="s">
+      <c r="L42" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="M42" s="56">
+      <c r="M42" s="50">
         <v>34</v>
       </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="41"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="41"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="49"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="22"/>
-      <c r="H43" s="53"/>
+      <c r="H43" s="45"/>
       <c r="I43" s="20"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
       <c r="N43" s="20"/>
     </row>
     <row r="44" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A44" s="40">
+      <c r="A44" s="55">
         <v>1</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="86">
+      <c r="C44" s="58">
         <v>46304</v>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="55">
         <v>1</v>
       </c>
       <c r="E44" s="11" t="s">
@@ -3850,52 +3850,52 @@
       <c r="G44" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="59" t="str">
+      <c r="H44" s="60" t="str">
         <f>G44</f>
         <v>BEPPU</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="J44" s="54" t="s">
+      <c r="J44" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="K44" s="45" t="s">
+      <c r="K44" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="L44" s="77" t="s">
+      <c r="L44" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="M44" s="56">
+      <c r="M44" s="50">
         <v>34</v>
       </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="41"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="49"/>
       <c r="E45" s="28"/>
       <c r="F45" s="9"/>
       <c r="G45" s="22"/>
-      <c r="H45" s="53"/>
+      <c r="H45" s="45"/>
       <c r="I45" s="20"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="49"/>
+      <c r="M45" s="49"/>
       <c r="N45" s="20"/>
     </row>
     <row r="46" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A46" s="57"/>
-      <c r="B46" s="58" t="s">
+      <c r="A46" s="63"/>
+      <c r="B46" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="86">
+      <c r="C46" s="58">
         <v>46305</v>
       </c>
-      <c r="D46" s="57"/>
+      <c r="D46" s="63"/>
       <c r="E46" s="11" t="s">
         <v>13</v>
       </c>
@@ -3905,23 +3905,23 @@
       <c r="G46" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="59" t="str">
+      <c r="H46" s="60" t="str">
         <f>G46</f>
         <v>YUFUIN</v>
       </c>
       <c r="I46" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J46" s="60" t="s">
+      <c r="J46" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="K46" s="45" t="s">
+      <c r="K46" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="L46" s="77" t="s">
+      <c r="L46" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="M46" s="56">
+      <c r="M46" s="50">
         <v>55</v>
       </c>
       <c r="N46" s="17" t="s">
@@ -3929,32 +3929,32 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="41"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="41"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="49"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
-      <c r="H47" s="53"/>
+      <c r="H47" s="45"/>
       <c r="I47" s="20"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="38"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="49"/>
+      <c r="M47" s="49"/>
       <c r="N47" s="20" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A48" s="57"/>
-      <c r="B48" s="58" t="s">
+      <c r="A48" s="63"/>
+      <c r="B48" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="86">
+      <c r="C48" s="58">
         <v>46306</v>
       </c>
-      <c r="D48" s="57"/>
+      <c r="D48" s="63"/>
       <c r="E48" s="11" t="s">
         <v>15</v>
       </c>
@@ -3964,23 +3964,23 @@
       <c r="G48" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="59" t="str">
+      <c r="H48" s="60" t="str">
         <f>G48</f>
         <v>KUMAMOTO</v>
       </c>
       <c r="I48" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="J48" s="54" t="s">
+      <c r="J48" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="K48" s="45" t="s">
+      <c r="K48" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="L48" s="55">
+      <c r="L48" s="48">
         <v>46304</v>
       </c>
-      <c r="M48" s="56">
+      <c r="M48" s="50">
         <v>32</v>
       </c>
       <c r="N48" s="17" t="s">
@@ -3988,32 +3988,32 @@
       </c>
     </row>
     <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="41"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="41"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="49"/>
       <c r="E49" s="14"/>
       <c r="F49" s="9"/>
       <c r="G49" s="22"/>
-      <c r="H49" s="53"/>
+      <c r="H49" s="45"/>
       <c r="I49" s="20"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="49"/>
+      <c r="M49" s="49"/>
       <c r="N49" s="20"/>
     </row>
     <row r="50" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A50" s="40">
+      <c r="A50" s="55">
         <v>1</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="84">
+      <c r="C50" s="66">
         <v>46307</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="55">
         <v>1</v>
       </c>
       <c r="E50" s="11" t="s">
@@ -4023,23 +4023,23 @@
       <c r="G50" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H50" s="59" t="str">
+      <c r="H50" s="60" t="str">
         <f>G50</f>
         <v>MINAMIASO</v>
       </c>
       <c r="I50" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="J50" s="60" t="s">
+      <c r="J50" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="K50" s="51" t="s">
+      <c r="K50" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="L50" s="55">
+      <c r="L50" s="48">
         <v>46302</v>
       </c>
-      <c r="M50" s="56">
+      <c r="M50" s="50">
         <v>52</v>
       </c>
       <c r="N50" s="25" t="s">
@@ -4047,10 +4047,10 @@
       </c>
     </row>
     <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="41"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="29" t="s">
         <v>125</v>
       </c>
@@ -4058,27 +4058,27 @@
         <v>126</v>
       </c>
       <c r="G51" s="22"/>
-      <c r="H51" s="53"/>
+      <c r="H51" s="45"/>
       <c r="I51" s="30"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="38"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="47"/>
+      <c r="L51" s="49"/>
+      <c r="M51" s="49"/>
       <c r="N51" s="30" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A52" s="40">
+      <c r="A52" s="55">
         <v>1</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="84">
+      <c r="C52" s="66">
         <v>46308</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="55">
         <v>1</v>
       </c>
       <c r="E52" s="11"/>
@@ -4086,54 +4086,54 @@
       <c r="G52" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H52" s="59" t="str">
+      <c r="H52" s="60" t="str">
         <f>G52</f>
         <v>KUROKAWA ONSEN</v>
       </c>
       <c r="I52" s="17"/>
-      <c r="J52" s="65" t="s">
+      <c r="J52" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="K52" s="46" t="s">
+      <c r="K52" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="L52" s="55">
+      <c r="L52" s="48">
         <v>46293</v>
       </c>
-      <c r="M52" s="76">
+      <c r="M52" s="65">
         <v>52</v>
       </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="41"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="41"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="49"/>
       <c r="E53" s="9" t="s">
         <v>130</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="22"/>
-      <c r="H53" s="53"/>
+      <c r="H53" s="45"/>
       <c r="I53" s="20"/>
-      <c r="J53" s="53"/>
-      <c r="K53" s="47"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="49"/>
       <c r="N53" s="20"/>
     </row>
     <row r="54" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="40">
+      <c r="A54" s="55">
         <v>1</v>
       </c>
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="84">
+      <c r="C54" s="66">
         <v>46309</v>
       </c>
-      <c r="D54" s="40">
+      <c r="D54" s="55">
         <v>1</v>
       </c>
       <c r="E54" s="11" t="s">
@@ -4143,21 +4143,21 @@
       <c r="G54" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H54" s="59" t="str">
+      <c r="H54" s="60" t="str">
         <f>G54</f>
         <v>TAKACHIHO</v>
       </c>
       <c r="I54" s="25"/>
-      <c r="J54" s="60" t="s">
+      <c r="J54" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="K54" s="49" t="s">
+      <c r="K54" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="L54" s="55">
+      <c r="L54" s="48">
         <v>46307</v>
       </c>
-      <c r="M54" s="56">
+      <c r="M54" s="50">
         <v>56</v>
       </c>
       <c r="N54" s="25" t="s">
@@ -4165,34 +4165,34 @@
       </c>
     </row>
     <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="41"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="41"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="49"/>
       <c r="E55" s="9" t="s">
         <v>130</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="22"/>
-      <c r="H55" s="53"/>
+      <c r="H55" s="45"/>
       <c r="I55" s="20"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="47"/>
+      <c r="L55" s="49"/>
+      <c r="M55" s="49"/>
       <c r="N55" s="20"/>
     </row>
     <row r="56" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A56" s="40">
+      <c r="A56" s="55">
         <v>1</v>
       </c>
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="84">
+      <c r="C56" s="66">
         <v>46310</v>
       </c>
-      <c r="D56" s="40">
+      <c r="D56" s="55">
         <v>1</v>
       </c>
       <c r="E56" s="11" t="s">
@@ -4202,21 +4202,21 @@
       <c r="G56" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H56" s="59" t="str">
+      <c r="H56" s="60" t="str">
         <f>G56</f>
         <v>KUMAMOTO</v>
       </c>
       <c r="I56" s="17"/>
-      <c r="J56" s="54" t="s">
+      <c r="J56" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="K56" s="45" t="s">
+      <c r="K56" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="L56" s="55">
+      <c r="L56" s="48">
         <v>46308</v>
       </c>
-      <c r="M56" s="56">
+      <c r="M56" s="50">
         <v>22</v>
       </c>
       <c r="N56" s="17" t="s">
@@ -4224,10 +4224,10 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="41"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="41"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="49"/>
       <c r="E57" s="9" t="s">
         <v>130</v>
       </c>
@@ -4235,25 +4235,25 @@
       <c r="G57" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="H57" s="53"/>
+      <c r="H57" s="45"/>
       <c r="I57" s="20"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="41"/>
+      <c r="J57" s="45"/>
+      <c r="K57" s="47"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="49"/>
       <c r="N57" s="20"/>
     </row>
     <row r="58" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A58" s="40">
+      <c r="A58" s="55">
         <v>1</v>
       </c>
-      <c r="B58" s="42" t="s">
+      <c r="B58" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="86">
+      <c r="C58" s="58">
         <v>46311</v>
       </c>
-      <c r="D58" s="40">
+      <c r="D58" s="55">
         <v>1</v>
       </c>
       <c r="E58" s="11"/>
@@ -4261,21 +4261,21 @@
       <c r="G58" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="59" t="str">
+      <c r="H58" s="60" t="str">
         <f>G58</f>
         <v>UNZEN</v>
       </c>
       <c r="I58" s="17"/>
-      <c r="J58" s="60" t="s">
+      <c r="J58" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="K58" s="66" t="s">
+      <c r="K58" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="L58" s="55">
+      <c r="L58" s="48">
         <v>46303</v>
       </c>
-      <c r="M58" s="56">
+      <c r="M58" s="50">
         <v>63</v>
       </c>
       <c r="N58" s="17" t="s">
@@ -4283,10 +4283,10 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="41"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="41"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="49"/>
       <c r="E59" s="9" t="s">
         <v>139</v>
       </c>
@@ -4294,25 +4294,25 @@
       <c r="G59" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="H59" s="53"/>
+      <c r="H59" s="45"/>
       <c r="I59" s="18"/>
-      <c r="J59" s="53"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="41"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="49"/>
+      <c r="M59" s="49"/>
       <c r="N59" s="18" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A60" s="57"/>
-      <c r="B60" s="58" t="s">
+      <c r="A60" s="63"/>
+      <c r="B60" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="86">
+      <c r="C60" s="58">
         <v>46312</v>
       </c>
-      <c r="D60" s="57"/>
+      <c r="D60" s="63"/>
       <c r="E60" s="11" t="s">
         <v>23</v>
       </c>
@@ -4320,21 +4320,21 @@
       <c r="G60" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H60" s="59" t="str">
+      <c r="H60" s="60" t="str">
         <f>G60</f>
         <v>OBAMA ONSEN</v>
       </c>
       <c r="I60" s="17"/>
-      <c r="J60" s="65" t="s">
+      <c r="J60" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K60" s="45" t="s">
+      <c r="K60" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="L60" s="55">
+      <c r="L60" s="48">
         <v>46310</v>
       </c>
-      <c r="M60" s="56">
+      <c r="M60" s="50">
         <v>50</v>
       </c>
       <c r="N60" s="17" t="s">
@@ -4342,50 +4342,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A61" s="41"/>
-      <c r="B61" s="39"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="41"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="49"/>
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
-      <c r="H61" s="53"/>
+      <c r="H61" s="45"/>
       <c r="I61" s="20"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="38"/>
-      <c r="L61" s="41"/>
-      <c r="M61" s="41"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="49"/>
+      <c r="M61" s="49"/>
       <c r="N61" s="20"/>
     </row>
     <row r="62" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A62" s="57"/>
-      <c r="B62" s="58" t="s">
+      <c r="A62" s="63"/>
+      <c r="B62" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C62" s="86">
+      <c r="C62" s="58">
         <v>46313</v>
       </c>
-      <c r="D62" s="57"/>
+      <c r="D62" s="63"/>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
       <c r="G62" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="59" t="str">
+      <c r="H62" s="60" t="str">
         <f>G62</f>
         <v>NAGASAKI</v>
       </c>
       <c r="I62" s="17"/>
-      <c r="J62" s="60" t="s">
+      <c r="J62" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="K62" s="46" t="s">
+      <c r="K62" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="L62" s="55">
+      <c r="L62" s="48">
         <v>46311</v>
       </c>
-      <c r="M62" s="56">
+      <c r="M62" s="50">
         <v>34</v>
       </c>
       <c r="N62" s="17" t="s">
@@ -4393,32 +4393,32 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A63" s="41"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="41"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="49"/>
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
-      <c r="H63" s="53"/>
+      <c r="H63" s="45"/>
       <c r="I63" s="20"/>
-      <c r="J63" s="53"/>
-      <c r="K63" s="47"/>
-      <c r="L63" s="41"/>
-      <c r="M63" s="41"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="53"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="49"/>
       <c r="N63" s="20"/>
     </row>
     <row r="64" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A64" s="40">
+      <c r="A64" s="55">
         <v>1</v>
       </c>
-      <c r="B64" s="42" t="s">
+      <c r="B64" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="86">
+      <c r="C64" s="58">
         <v>46314</v>
       </c>
-      <c r="D64" s="40">
+      <c r="D64" s="55">
         <v>1</v>
       </c>
       <c r="E64" s="11" t="s">
@@ -4430,21 +4430,21 @@
       <c r="G64" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="59" t="str">
+      <c r="H64" s="60" t="str">
         <f>G64</f>
         <v>NAGASAKI</v>
       </c>
       <c r="I64" s="17"/>
-      <c r="J64" s="60" t="s">
+      <c r="J64" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="K64" s="46" t="s">
+      <c r="K64" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="L64" s="55">
+      <c r="L64" s="48">
         <v>46311</v>
       </c>
-      <c r="M64" s="56">
+      <c r="M64" s="50">
         <v>34</v>
       </c>
       <c r="N64" s="17" t="s">
@@ -4452,32 +4452,32 @@
       </c>
     </row>
     <row r="65" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="41"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="41"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="49"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="22"/>
-      <c r="H65" s="53"/>
+      <c r="H65" s="45"/>
       <c r="I65" s="20"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="47"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="41"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="49"/>
+      <c r="M65" s="49"/>
       <c r="N65" s="20"/>
     </row>
     <row r="66" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A66" s="40">
+      <c r="A66" s="55">
         <v>1</v>
       </c>
-      <c r="B66" s="42" t="s">
+      <c r="B66" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="86">
+      <c r="C66" s="58">
         <v>46315</v>
       </c>
-      <c r="D66" s="40">
+      <c r="D66" s="55">
         <v>1</v>
       </c>
       <c r="E66" s="11" t="s">
@@ -4489,21 +4489,21 @@
       <c r="G66" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H66" s="59" t="str">
+      <c r="H66" s="60" t="str">
         <f>G66</f>
         <v>URESHINO</v>
       </c>
       <c r="I66" s="17"/>
-      <c r="J66" s="65" t="s">
+      <c r="J66" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="K66" s="45" t="s">
+      <c r="K66" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="L66" s="55">
+      <c r="L66" s="48">
         <v>46307</v>
       </c>
-      <c r="M66" s="56">
+      <c r="M66" s="50">
         <v>37</v>
       </c>
       <c r="N66" s="17" t="s">
@@ -4511,32 +4511,32 @@
       </c>
     </row>
     <row r="67" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="41"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="41"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="49"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="22"/>
-      <c r="H67" s="53"/>
+      <c r="H67" s="45"/>
       <c r="I67" s="20"/>
-      <c r="J67" s="53"/>
-      <c r="K67" s="38"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="41"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="47"/>
+      <c r="L67" s="49"/>
+      <c r="M67" s="49"/>
       <c r="N67" s="20"/>
     </row>
     <row r="68" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A68" s="40">
+      <c r="A68" s="55">
         <v>1</v>
       </c>
-      <c r="B68" s="42" t="s">
+      <c r="B68" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C68" s="86">
+      <c r="C68" s="58">
         <v>46316</v>
       </c>
-      <c r="D68" s="40">
+      <c r="D68" s="55">
         <v>1</v>
       </c>
       <c r="E68" s="11" t="s">
@@ -4548,21 +4548,21 @@
       <c r="G68" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H68" s="59" t="str">
+      <c r="H68" s="60" t="str">
         <f>G68</f>
         <v>FUKUOKA</v>
       </c>
       <c r="I68" s="17"/>
-      <c r="J68" s="60" t="s">
+      <c r="J68" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K68" s="66" t="s">
+      <c r="K68" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="L68" s="55">
+      <c r="L68" s="48">
         <v>46313</v>
       </c>
-      <c r="M68" s="56">
+      <c r="M68" s="50">
         <v>57</v>
       </c>
       <c r="N68" s="17" t="s">
@@ -4570,32 +4570,32 @@
       </c>
     </row>
     <row r="69" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="41"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="41"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="49"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="22"/>
-      <c r="H69" s="53"/>
+      <c r="H69" s="45"/>
       <c r="I69" s="20"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="38"/>
-      <c r="L69" s="41"/>
-      <c r="M69" s="41"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="47"/>
+      <c r="L69" s="49"/>
+      <c r="M69" s="49"/>
       <c r="N69" s="20"/>
     </row>
     <row r="70" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A70" s="40">
+      <c r="A70" s="55">
         <v>1</v>
       </c>
-      <c r="B70" s="42" t="s">
+      <c r="B70" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C70" s="86">
+      <c r="C70" s="58">
         <v>46317</v>
       </c>
-      <c r="D70" s="40">
+      <c r="D70" s="55">
         <v>1</v>
       </c>
       <c r="E70" s="11" t="s">
@@ -4607,21 +4607,21 @@
       <c r="G70" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H70" s="59" t="str">
+      <c r="H70" s="60" t="str">
         <f>G70</f>
         <v>FUKUOKA</v>
       </c>
       <c r="I70" s="17"/>
-      <c r="J70" s="60" t="s">
+      <c r="J70" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K70" s="66" t="s">
+      <c r="K70" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="L70" s="55">
+      <c r="L70" s="48">
         <v>46313</v>
       </c>
-      <c r="M70" s="56">
+      <c r="M70" s="50">
         <v>57</v>
       </c>
       <c r="N70" s="17" t="s">
@@ -4629,34 +4629,34 @@
       </c>
     </row>
     <row r="71" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="41"/>
-      <c r="B71" s="39"/>
-      <c r="C71" s="85"/>
-      <c r="D71" s="41"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="49"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9" t="s">
         <v>151</v>
       </c>
       <c r="G71" s="22"/>
-      <c r="H71" s="53"/>
+      <c r="H71" s="45"/>
       <c r="I71" s="20"/>
-      <c r="J71" s="53"/>
-      <c r="K71" s="38"/>
-      <c r="L71" s="41"/>
-      <c r="M71" s="41"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="47"/>
+      <c r="L71" s="49"/>
+      <c r="M71" s="49"/>
       <c r="N71" s="20"/>
     </row>
     <row r="72" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A72" s="40">
+      <c r="A72" s="55">
         <v>1</v>
       </c>
-      <c r="B72" s="42" t="s">
+      <c r="B72" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C72" s="86">
+      <c r="C72" s="58">
         <v>46318</v>
       </c>
-      <c r="D72" s="40">
+      <c r="D72" s="55">
         <v>1</v>
       </c>
       <c r="E72" s="11" t="s">
@@ -4668,23 +4668,23 @@
       <c r="G72" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H72" s="59" t="str">
+      <c r="H72" s="60" t="str">
         <f>G72</f>
         <v>TOKYO</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="J72" s="67" t="s">
+      <c r="J72" s="85" t="s">
         <v>154</v>
       </c>
-      <c r="K72" s="50" t="s">
+      <c r="K72" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L72" s="68">
+      <c r="L72" s="82">
         <v>46315</v>
       </c>
-      <c r="M72" s="56">
+      <c r="M72" s="50">
         <v>65</v>
       </c>
       <c r="N72" s="12" t="s">
@@ -4692,10 +4692,10 @@
       </c>
     </row>
     <row r="73" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A73" s="41"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="41"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="49"/>
       <c r="E73" s="9"/>
       <c r="F73" s="13" t="s">
         <v>156</v>
@@ -4703,25 +4703,25 @@
       <c r="G73" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="H73" s="53"/>
+      <c r="H73" s="45"/>
       <c r="I73" s="15"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="38"/>
-      <c r="L73" s="41"/>
-      <c r="M73" s="41"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="49"/>
       <c r="N73" s="33" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A74" s="57"/>
-      <c r="B74" s="58" t="s">
+      <c r="A74" s="63"/>
+      <c r="B74" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="86">
+      <c r="C74" s="58">
         <v>46319</v>
       </c>
-      <c r="D74" s="57"/>
+      <c r="D74" s="63"/>
       <c r="E74" s="11" t="s">
         <v>30</v>
       </c>
@@ -4731,23 +4731,23 @@
       <c r="G74" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H74" s="59" t="str">
+      <c r="H74" s="60" t="str">
         <f>G74</f>
         <v>TOKYO</v>
       </c>
       <c r="I74" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="J74" s="67" t="s">
+      <c r="J74" s="85" t="s">
         <v>154</v>
       </c>
-      <c r="K74" s="50" t="s">
+      <c r="K74" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L74" s="68">
+      <c r="L74" s="82">
         <v>46315</v>
       </c>
-      <c r="M74" s="56">
+      <c r="M74" s="50">
         <v>65</v>
       </c>
       <c r="N74" s="12" t="s">
@@ -4755,10 +4755,10 @@
       </c>
     </row>
     <row r="75" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A75" s="41"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="41"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="49"/>
       <c r="E75" s="14"/>
       <c r="F75" s="14" t="s">
         <v>163</v>
@@ -4766,23 +4766,23 @@
       <c r="G75" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H75" s="53"/>
+      <c r="H75" s="45"/>
       <c r="I75" s="20"/>
-      <c r="J75" s="53"/>
-      <c r="K75" s="38"/>
-      <c r="L75" s="41"/>
-      <c r="M75" s="41"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="47"/>
+      <c r="L75" s="49"/>
+      <c r="M75" s="49"/>
       <c r="N75" s="20"/>
     </row>
     <row r="76" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A76" s="57"/>
-      <c r="B76" s="58" t="s">
+      <c r="A76" s="63"/>
+      <c r="B76" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="86">
+      <c r="C76" s="58">
         <v>46320</v>
       </c>
-      <c r="D76" s="57"/>
+      <c r="D76" s="63"/>
       <c r="E76" s="11" t="s">
         <v>30</v>
       </c>
@@ -4792,21 +4792,21 @@
       <c r="G76" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H76" s="59" t="str">
+      <c r="H76" s="60" t="str">
         <f>G76</f>
         <v>TOKYO</v>
       </c>
       <c r="I76" s="12"/>
-      <c r="J76" s="67" t="s">
+      <c r="J76" s="85" t="s">
         <v>154</v>
       </c>
-      <c r="K76" s="50" t="s">
+      <c r="K76" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L76" s="68">
+      <c r="L76" s="82">
         <v>46315</v>
       </c>
-      <c r="M76" s="56">
+      <c r="M76" s="50">
         <v>65</v>
       </c>
       <c r="N76" s="12" t="s">
@@ -4814,10 +4814,10 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A77" s="41"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="85"/>
-      <c r="D77" s="41"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="57"/>
+      <c r="C77" s="59"/>
+      <c r="D77" s="49"/>
       <c r="E77" s="14"/>
       <c r="F77" s="14" t="s">
         <v>163</v>
@@ -4825,27 +4825,27 @@
       <c r="G77" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H77" s="53"/>
+      <c r="H77" s="45"/>
       <c r="I77" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="J77" s="53"/>
-      <c r="K77" s="38"/>
-      <c r="L77" s="41"/>
-      <c r="M77" s="41"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="47"/>
+      <c r="L77" s="49"/>
+      <c r="M77" s="49"/>
       <c r="N77" s="20"/>
     </row>
     <row r="78" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A78" s="40">
+      <c r="A78" s="55">
         <v>1</v>
       </c>
-      <c r="B78" s="42" t="s">
+      <c r="B78" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="86">
+      <c r="C78" s="58">
         <v>46321</v>
       </c>
-      <c r="D78" s="61">
+      <c r="D78" s="69">
         <v>0</v>
       </c>
       <c r="E78" s="11" t="s">
@@ -4857,24 +4857,24 @@
       <c r="G78" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="H78" s="71" t="str">
+      <c r="H78" s="84" t="str">
         <f>G78</f>
         <v>Hokkawa/Akazawa</v>
       </c>
       <c r="I78" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="J78" s="60"/>
-      <c r="K78" s="69"/>
-      <c r="L78" s="55"/>
-      <c r="M78" s="56"/>
+      <c r="J78" s="51"/>
+      <c r="K78" s="83"/>
+      <c r="L78" s="48"/>
+      <c r="M78" s="50"/>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="41"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="85"/>
-      <c r="D79" s="41"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="49"/>
       <c r="E79" s="9" t="s">
         <v>193</v>
       </c>
@@ -4884,25 +4884,25 @@
       <c r="G79" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="H79" s="53"/>
+      <c r="H79" s="45"/>
       <c r="I79" s="20"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="38"/>
-      <c r="L79" s="41"/>
-      <c r="M79" s="41"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="47"/>
+      <c r="L79" s="49"/>
+      <c r="M79" s="49"/>
       <c r="N79" s="20"/>
     </row>
     <row r="80" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A80" s="40">
+      <c r="A80" s="55">
         <v>1</v>
       </c>
-      <c r="B80" s="42" t="s">
+      <c r="B80" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C80" s="86">
+      <c r="C80" s="58">
         <v>46322</v>
       </c>
-      <c r="D80" s="61">
+      <c r="D80" s="69">
         <v>0</v>
       </c>
       <c r="E80" s="32" t="s">
@@ -4914,48 +4914,48 @@
       <c r="G80" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="H80" s="71" t="str">
+      <c r="H80" s="84" t="str">
         <f>G80</f>
         <v>Fujinomiya</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="J80" s="60"/>
-      <c r="K80" s="69"/>
-      <c r="L80" s="55"/>
-      <c r="M80" s="56"/>
+      <c r="J80" s="51"/>
+      <c r="K80" s="83"/>
+      <c r="L80" s="48"/>
+      <c r="M80" s="50"/>
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A81" s="41"/>
-      <c r="B81" s="39"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="41"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="49"/>
       <c r="E81" s="9" t="s">
         <v>130</v>
       </c>
       <c r="F81" s="9"/>
       <c r="G81" s="22"/>
-      <c r="H81" s="53"/>
+      <c r="H81" s="45"/>
       <c r="I81" s="20"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="38"/>
-      <c r="L81" s="41"/>
-      <c r="M81" s="41"/>
+      <c r="J81" s="45"/>
+      <c r="K81" s="47"/>
+      <c r="L81" s="49"/>
+      <c r="M81" s="49"/>
       <c r="N81" s="20"/>
     </row>
     <row r="82" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A82" s="70">
+      <c r="A82" s="77">
         <v>1</v>
       </c>
-      <c r="B82" s="42" t="s">
+      <c r="B82" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C82" s="86">
+      <c r="C82" s="58">
         <v>46323</v>
       </c>
-      <c r="D82" s="61">
+      <c r="D82" s="69">
         <v>0</v>
       </c>
       <c r="E82" s="11"/>
@@ -4963,48 +4963,48 @@
       <c r="G82" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="H82" s="71" t="str">
+      <c r="H82" s="84" t="str">
         <f>G82</f>
         <v>Hottarakashi</v>
       </c>
       <c r="I82" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="J82" s="60"/>
-      <c r="K82" s="69"/>
-      <c r="L82" s="55"/>
-      <c r="M82" s="56"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="83"/>
+      <c r="L82" s="48"/>
+      <c r="M82" s="50"/>
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="41"/>
-      <c r="B83" s="39"/>
-      <c r="C83" s="85"/>
-      <c r="D83" s="41"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="49"/>
       <c r="E83" s="9" t="s">
         <v>130</v>
       </c>
       <c r="F83" s="9"/>
       <c r="G83" s="22"/>
-      <c r="H83" s="53"/>
+      <c r="H83" s="45"/>
       <c r="I83" s="20"/>
-      <c r="J83" s="53"/>
-      <c r="K83" s="38"/>
-      <c r="L83" s="41"/>
-      <c r="M83" s="41"/>
+      <c r="J83" s="45"/>
+      <c r="K83" s="47"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="49"/>
       <c r="N83" s="20"/>
     </row>
     <row r="84" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A84" s="70">
+      <c r="A84" s="77">
         <v>1</v>
       </c>
-      <c r="B84" s="42" t="s">
+      <c r="B84" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C84" s="86">
+      <c r="C84" s="58">
         <v>46324</v>
       </c>
-      <c r="D84" s="61">
+      <c r="D84" s="69">
         <v>0</v>
       </c>
       <c r="E84" s="11"/>
@@ -5014,22 +5014,22 @@
       <c r="G84" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H84" s="71" t="str">
+      <c r="H84" s="84" t="str">
         <f>G84</f>
         <v>TOKYO</v>
       </c>
       <c r="I84" s="17"/>
-      <c r="J84" s="60"/>
-      <c r="K84" s="69"/>
-      <c r="L84" s="55"/>
-      <c r="M84" s="56"/>
+      <c r="J84" s="51"/>
+      <c r="K84" s="83"/>
+      <c r="L84" s="48"/>
+      <c r="M84" s="50"/>
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="41"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="85"/>
-      <c r="D85" s="41"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="49"/>
       <c r="E85" s="9" t="s">
         <v>201</v>
       </c>
@@ -5037,25 +5037,25 @@
         <v>168</v>
       </c>
       <c r="G85" s="22"/>
-      <c r="H85" s="53"/>
+      <c r="H85" s="45"/>
       <c r="I85" s="20"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="38"/>
-      <c r="L85" s="41"/>
-      <c r="M85" s="41"/>
+      <c r="J85" s="45"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="49"/>
+      <c r="M85" s="49"/>
       <c r="N85" s="20"/>
     </row>
     <row r="86" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A86" s="70">
+      <c r="A86" s="77">
         <v>1</v>
       </c>
-      <c r="B86" s="42" t="s">
+      <c r="B86" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C86" s="86">
+      <c r="C86" s="58">
         <v>46325</v>
       </c>
-      <c r="D86" s="40">
+      <c r="D86" s="55">
         <v>1</v>
       </c>
       <c r="E86" s="11" t="s">
@@ -5067,23 +5067,23 @@
       <c r="G86" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H86" s="59" t="str">
+      <c r="H86" s="60" t="str">
         <f>G86</f>
         <v>TOKYO</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="J86" s="72" t="s">
+      <c r="J86" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="K86" s="50" t="s">
+      <c r="K86" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L86" s="68">
+      <c r="L86" s="82">
         <v>46322</v>
       </c>
-      <c r="M86" s="56">
+      <c r="M86" s="50">
         <v>65</v>
       </c>
       <c r="N86" s="12" t="s">
@@ -5091,34 +5091,34 @@
       </c>
     </row>
     <row r="87" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A87" s="41"/>
-      <c r="B87" s="39"/>
-      <c r="C87" s="85"/>
-      <c r="D87" s="41"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="59"/>
+      <c r="D87" s="49"/>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
       <c r="G87" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="H87" s="53"/>
+      <c r="H87" s="45"/>
       <c r="I87" s="15"/>
-      <c r="J87" s="53"/>
-      <c r="K87" s="38"/>
-      <c r="L87" s="41"/>
-      <c r="M87" s="41"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="47"/>
+      <c r="L87" s="49"/>
+      <c r="M87" s="49"/>
       <c r="N87" s="33" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A88" s="57"/>
-      <c r="B88" s="58" t="s">
+      <c r="A88" s="63"/>
+      <c r="B88" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="86">
+      <c r="C88" s="58">
         <v>46326</v>
       </c>
-      <c r="D88" s="57"/>
+      <c r="D88" s="63"/>
       <c r="E88" s="11" t="s">
         <v>30</v>
       </c>
@@ -5128,23 +5128,23 @@
       <c r="G88" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H88" s="59" t="str">
+      <c r="H88" s="60" t="str">
         <f>G88</f>
         <v>TOKYO</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="J88" s="72" t="s">
+      <c r="J88" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="K88" s="50" t="s">
+      <c r="K88" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L88" s="68">
+      <c r="L88" s="82">
         <v>46322</v>
       </c>
-      <c r="M88" s="56">
+      <c r="M88" s="50">
         <v>65</v>
       </c>
       <c r="N88" s="12" t="s">
@@ -5152,32 +5152,32 @@
       </c>
     </row>
     <row r="89" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A89" s="41"/>
-      <c r="B89" s="39"/>
-      <c r="C89" s="85"/>
-      <c r="D89" s="41"/>
+      <c r="A89" s="49"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="49"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
       <c r="G89" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="H89" s="53"/>
+      <c r="H89" s="45"/>
       <c r="I89" s="20"/>
-      <c r="J89" s="53"/>
-      <c r="K89" s="38"/>
-      <c r="L89" s="41"/>
-      <c r="M89" s="41"/>
+      <c r="J89" s="45"/>
+      <c r="K89" s="47"/>
+      <c r="L89" s="49"/>
+      <c r="M89" s="49"/>
       <c r="N89" s="20"/>
     </row>
     <row r="90" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A90" s="57"/>
-      <c r="B90" s="58" t="s">
+      <c r="A90" s="63"/>
+      <c r="B90" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="86">
+      <c r="C90" s="58">
         <v>46327</v>
       </c>
-      <c r="D90" s="57"/>
+      <c r="D90" s="63"/>
       <c r="E90" s="11" t="s">
         <v>30</v>
       </c>
@@ -5187,23 +5187,23 @@
       <c r="G90" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H90" s="59" t="str">
+      <c r="H90" s="60" t="str">
         <f>G90</f>
         <v>TOKYO</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="J90" s="72" t="s">
+      <c r="J90" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="K90" s="50" t="s">
+      <c r="K90" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="L90" s="68">
+      <c r="L90" s="82">
         <v>46322</v>
       </c>
-      <c r="M90" s="56">
+      <c r="M90" s="50">
         <v>65</v>
       </c>
       <c r="N90" s="12" t="s">
@@ -5211,10 +5211,10 @@
       </c>
     </row>
     <row r="91" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A91" s="41"/>
-      <c r="B91" s="39"/>
-      <c r="C91" s="85"/>
-      <c r="D91" s="41"/>
+      <c r="A91" s="49"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="59"/>
+      <c r="D91" s="49"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14" t="s">
         <v>176</v>
@@ -5222,25 +5222,25 @@
       <c r="G91" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="H91" s="53"/>
+      <c r="H91" s="45"/>
       <c r="I91" s="20"/>
-      <c r="J91" s="53"/>
-      <c r="K91" s="38"/>
-      <c r="L91" s="41"/>
-      <c r="M91" s="41"/>
+      <c r="J91" s="45"/>
+      <c r="K91" s="47"/>
+      <c r="L91" s="49"/>
+      <c r="M91" s="49"/>
       <c r="N91" s="20"/>
     </row>
     <row r="92" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A92" s="62">
+      <c r="A92" s="79">
         <v>0</v>
       </c>
-      <c r="B92" s="42" t="s">
+      <c r="B92" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C92" s="86">
+      <c r="C92" s="58">
         <v>46328</v>
       </c>
-      <c r="D92" s="62">
+      <c r="D92" s="79">
         <v>0</v>
       </c>
       <c r="E92" s="7" t="s">
@@ -5252,23 +5252,23 @@
       <c r="G92" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="H92" s="59" t="str">
+      <c r="H92" s="60" t="str">
         <f>G92</f>
         <v>MIYAKOJIMA</v>
       </c>
       <c r="I92" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="J92" s="60" t="s">
+      <c r="J92" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="K92" s="48" t="s">
+      <c r="K92" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="L92" s="55">
+      <c r="L92" s="48">
         <v>46317</v>
       </c>
-      <c r="M92" s="56">
+      <c r="M92" s="50">
         <v>68</v>
       </c>
       <c r="N92" s="17" t="s">
@@ -5276,10 +5276,10 @@
       </c>
     </row>
     <row r="93" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A93" s="41"/>
-      <c r="B93" s="39"/>
-      <c r="C93" s="85"/>
-      <c r="D93" s="41"/>
+      <c r="A93" s="49"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="49"/>
       <c r="E93" s="13" t="s">
         <v>204</v>
       </c>
@@ -5287,25 +5287,25 @@
       <c r="G93" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="H93" s="53"/>
+      <c r="H93" s="45"/>
       <c r="I93" s="20"/>
-      <c r="J93" s="53"/>
-      <c r="K93" s="38"/>
-      <c r="L93" s="41"/>
-      <c r="M93" s="41"/>
+      <c r="J93" s="45"/>
+      <c r="K93" s="47"/>
+      <c r="L93" s="49"/>
+      <c r="M93" s="49"/>
       <c r="N93" s="20"/>
     </row>
     <row r="94" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A94" s="62">
+      <c r="A94" s="79">
         <v>0</v>
       </c>
-      <c r="B94" s="42" t="s">
+      <c r="B94" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C94" s="86">
+      <c r="C94" s="58">
         <v>46329</v>
       </c>
-      <c r="D94" s="62">
+      <c r="D94" s="79">
         <v>0</v>
       </c>
       <c r="E94" s="11" t="s">
@@ -5317,32 +5317,32 @@
       <c r="G94" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="H94" s="59" t="str">
+      <c r="H94" s="60" t="str">
         <f>G94</f>
         <v>MIYAKOJIMA</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="J94" s="60" t="s">
+      <c r="J94" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="K94" s="48" t="s">
+      <c r="K94" s="71" t="s">
         <v>210</v>
       </c>
-      <c r="L94" s="55">
+      <c r="L94" s="48">
         <v>46317</v>
       </c>
-      <c r="M94" s="56">
+      <c r="M94" s="50">
         <v>68</v>
       </c>
       <c r="N94" s="17"/>
     </row>
     <row r="95" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" s="41"/>
-      <c r="B95" s="39"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="41"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="49"/>
       <c r="E95" s="9" t="s">
         <v>181</v>
       </c>
@@ -5350,27 +5350,27 @@
       <c r="G95" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="H95" s="53"/>
+      <c r="H95" s="45"/>
       <c r="I95" s="20"/>
-      <c r="J95" s="53"/>
-      <c r="K95" s="38"/>
-      <c r="L95" s="41"/>
-      <c r="M95" s="41"/>
+      <c r="J95" s="45"/>
+      <c r="K95" s="47"/>
+      <c r="L95" s="49"/>
+      <c r="M95" s="49"/>
       <c r="N95" s="30" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A96" s="62">
+      <c r="A96" s="79">
         <v>0</v>
       </c>
-      <c r="B96" s="42" t="s">
+      <c r="B96" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C96" s="86">
+      <c r="C96" s="58">
         <v>46330</v>
       </c>
-      <c r="D96" s="62">
+      <c r="D96" s="79">
         <v>0</v>
       </c>
       <c r="E96" s="11" t="s">
@@ -5382,56 +5382,56 @@
       <c r="G96" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="H96" s="59" t="str">
+      <c r="H96" s="60" t="str">
         <f>G96</f>
         <v>MIYAKOJIMA</v>
       </c>
       <c r="I96" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="J96" s="60" t="s">
+      <c r="J96" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="K96" s="45" t="s">
+      <c r="K96" s="46" t="s">
         <v>215</v>
       </c>
-      <c r="L96" s="55">
+      <c r="L96" s="48">
         <v>46329</v>
       </c>
-      <c r="M96" s="56">
+      <c r="M96" s="50">
         <v>36</v>
       </c>
       <c r="N96" s="17"/>
     </row>
     <row r="97" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A97" s="41"/>
-      <c r="B97" s="39"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="41"/>
+      <c r="A97" s="49"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="49"/>
       <c r="E97" s="9" t="s">
         <v>212</v>
       </c>
       <c r="F97" s="9"/>
       <c r="G97" s="22"/>
-      <c r="H97" s="53"/>
+      <c r="H97" s="45"/>
       <c r="I97" s="20"/>
-      <c r="J97" s="53"/>
-      <c r="K97" s="38"/>
-      <c r="L97" s="41"/>
-      <c r="M97" s="41"/>
+      <c r="J97" s="45"/>
+      <c r="K97" s="47"/>
+      <c r="L97" s="49"/>
+      <c r="M97" s="49"/>
       <c r="N97" s="20"/>
     </row>
     <row r="98" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A98" s="70">
+      <c r="A98" s="77">
         <v>1</v>
       </c>
-      <c r="B98" s="42" t="s">
+      <c r="B98" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C98" s="86">
+      <c r="C98" s="58">
         <v>46331</v>
       </c>
-      <c r="D98" s="40">
+      <c r="D98" s="55">
         <v>1</v>
       </c>
       <c r="E98" s="11" t="s">
@@ -5443,23 +5443,23 @@
       <c r="G98" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="H98" s="59" t="str">
+      <c r="H98" s="60" t="str">
         <f>G98</f>
         <v>NANJO</v>
       </c>
       <c r="I98" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="J98" s="60" t="s">
+      <c r="J98" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="K98" s="46" t="s">
+      <c r="K98" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="L98" s="55">
+      <c r="L98" s="48">
         <v>46316</v>
       </c>
-      <c r="M98" s="56">
+      <c r="M98" s="50">
         <v>50</v>
       </c>
       <c r="N98" s="17" t="s">
@@ -5467,10 +5467,10 @@
       </c>
     </row>
     <row r="99" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A99" s="41"/>
-      <c r="B99" s="39"/>
-      <c r="C99" s="85"/>
-      <c r="D99" s="41"/>
+      <c r="A99" s="49"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="49"/>
       <c r="E99" s="9" t="s">
         <v>218</v>
       </c>
@@ -5478,27 +5478,27 @@
         <v>219</v>
       </c>
       <c r="G99" s="22"/>
-      <c r="H99" s="53"/>
+      <c r="H99" s="45"/>
       <c r="I99" s="20"/>
-      <c r="J99" s="53"/>
-      <c r="K99" s="47"/>
-      <c r="L99" s="41"/>
-      <c r="M99" s="41"/>
+      <c r="J99" s="45"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="49"/>
+      <c r="M99" s="49"/>
       <c r="N99" s="30" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A100" s="70">
+      <c r="A100" s="77">
         <v>1</v>
       </c>
-      <c r="B100" s="42" t="s">
+      <c r="B100" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="86">
+      <c r="C100" s="58">
         <v>46332</v>
       </c>
-      <c r="D100" s="70">
+      <c r="D100" s="77">
         <v>1</v>
       </c>
       <c r="E100" s="11" t="s">
@@ -5510,54 +5510,54 @@
       <c r="G100" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H100" s="59" t="str">
+      <c r="H100" s="60" t="str">
         <f>G100</f>
         <v>NAHA</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="J100" s="60" t="s">
+      <c r="J100" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="K100" s="48" t="s">
+      <c r="K100" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="L100" s="73" t="s">
+      <c r="L100" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="M100" s="56">
+      <c r="M100" s="50">
         <v>32</v>
       </c>
       <c r="N100" s="17"/>
     </row>
     <row r="101" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="41"/>
-      <c r="B101" s="39"/>
-      <c r="C101" s="85"/>
-      <c r="D101" s="41"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="59"/>
+      <c r="D101" s="49"/>
       <c r="E101" s="9" t="s">
         <v>224</v>
       </c>
       <c r="F101" s="9"/>
       <c r="G101" s="22"/>
-      <c r="H101" s="53"/>
+      <c r="H101" s="45"/>
       <c r="I101" s="20"/>
-      <c r="J101" s="53"/>
-      <c r="K101" s="38"/>
-      <c r="L101" s="41"/>
-      <c r="M101" s="41"/>
+      <c r="J101" s="45"/>
+      <c r="K101" s="47"/>
+      <c r="L101" s="49"/>
+      <c r="M101" s="49"/>
       <c r="N101" s="20"/>
     </row>
     <row r="102" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A102" s="57"/>
-      <c r="B102" s="58" t="s">
+      <c r="A102" s="63"/>
+      <c r="B102" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C102" s="86">
+      <c r="C102" s="58">
         <v>46333</v>
       </c>
-      <c r="D102" s="57"/>
+      <c r="D102" s="63"/>
       <c r="E102" s="11" t="s">
         <v>38</v>
       </c>
@@ -5567,52 +5567,52 @@
       <c r="G102" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H102" s="59" t="str">
+      <c r="H102" s="60" t="str">
         <f>G102</f>
         <v>NAHA</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="J102" s="60" t="s">
+      <c r="J102" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="K102" s="48" t="s">
+      <c r="K102" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="L102" s="73" t="s">
+      <c r="L102" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="M102" s="56">
+      <c r="M102" s="50">
         <v>32</v>
       </c>
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A103" s="41"/>
-      <c r="B103" s="39"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="41"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="59"/>
+      <c r="D103" s="49"/>
       <c r="E103" s="14"/>
       <c r="F103" s="14"/>
       <c r="G103" s="14"/>
-      <c r="H103" s="53"/>
+      <c r="H103" s="45"/>
       <c r="I103" s="20"/>
-      <c r="J103" s="53"/>
-      <c r="K103" s="38"/>
-      <c r="L103" s="41"/>
-      <c r="M103" s="41"/>
+      <c r="J103" s="45"/>
+      <c r="K103" s="47"/>
+      <c r="L103" s="49"/>
+      <c r="M103" s="49"/>
       <c r="N103" s="20"/>
     </row>
     <row r="104" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A104" s="57"/>
-      <c r="B104" s="58" t="s">
+      <c r="A104" s="63"/>
+      <c r="B104" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C104" s="86">
+      <c r="C104" s="58">
         <v>46334</v>
       </c>
-      <c r="D104" s="57"/>
+      <c r="D104" s="63"/>
       <c r="E104" s="11" t="s">
         <v>38</v>
       </c>
@@ -5622,25 +5622,25 @@
       <c r="G104" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H104" s="43" t="s">
+      <c r="H104" s="78" t="s">
         <v>27</v>
       </c>
       <c r="I104" s="34"/>
       <c r="J104" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="K104" s="74">
+      <c r="K104" s="73">
         <f>SUM(M4:M103)</f>
         <v>2053</v>
       </c>
-      <c r="L104" s="44"/>
-      <c r="M104" s="37"/>
+      <c r="L104" s="74"/>
+      <c r="M104" s="75"/>
     </row>
     <row r="105" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A105" s="41"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="85"/>
-      <c r="D105" s="41"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="57"/>
+      <c r="C105" s="59"/>
+      <c r="D105" s="49"/>
       <c r="E105" s="14"/>
       <c r="F105" s="10" t="s">
         <v>188</v>
@@ -5648,30 +5648,30 @@
       <c r="G105" s="10">
         <v>0.97222222222222221</v>
       </c>
-      <c r="H105" s="38"/>
+      <c r="H105" s="47"/>
       <c r="I105" s="35"/>
       <c r="J105" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="K105" s="75">
+      <c r="K105" s="76">
         <f>AVERAGE(M4:M103)</f>
         <v>44.630434782608695</v>
       </c>
-      <c r="L105" s="41"/>
-      <c r="M105" s="39"/>
+      <c r="L105" s="49"/>
+      <c r="M105" s="57"/>
       <c r="N105" s="36"/>
     </row>
     <row r="106" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A106" s="70">
+      <c r="A106" s="77">
         <v>1</v>
       </c>
-      <c r="B106" s="42" t="s">
+      <c r="B106" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="C106" s="86">
+      <c r="C106" s="58">
         <v>46335</v>
       </c>
-      <c r="D106" s="70">
+      <c r="D106" s="77">
         <v>1</v>
       </c>
       <c r="E106" s="7" t="s">
@@ -5683,10 +5683,10 @@
       <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A107" s="41"/>
-      <c r="B107" s="39"/>
-      <c r="C107" s="85"/>
-      <c r="D107" s="41"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="59"/>
+      <c r="D107" s="49"/>
       <c r="E107" s="10">
         <v>0.28472222222222221</v>
       </c>
@@ -9068,90 +9068,366 @@
     <row r="950" spans="9:10" ht="13.2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="467">
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="K60:K61"/>
-    <mergeCell ref="L60:L61"/>
-    <mergeCell ref="M60:M61"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="K62:K63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="J64:J65"/>
-    <mergeCell ref="K64:K65"/>
-    <mergeCell ref="L64:L65"/>
-    <mergeCell ref="M64:M65"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="M54:M55"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="L52:L53"/>
-    <mergeCell ref="M52:M53"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="L50:L51"/>
-    <mergeCell ref="M50:M51"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="K46:K47"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="M46:M47"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="K48:K49"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="K42:K43"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="M68:M69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="L72:L73"/>
+    <mergeCell ref="M72:M73"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="M74:M75"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="M76:M77"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="L78:L79"/>
+    <mergeCell ref="M78:M79"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="K80:K81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="K84:K85"/>
+    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="M84:M85"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="K86:K87"/>
+    <mergeCell ref="L86:L87"/>
+    <mergeCell ref="M86:M87"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="M88:M89"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="K90:K91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="J92:J93"/>
+    <mergeCell ref="K92:K93"/>
+    <mergeCell ref="L92:L93"/>
+    <mergeCell ref="M92:M93"/>
+    <mergeCell ref="J94:J95"/>
+    <mergeCell ref="K94:K95"/>
+    <mergeCell ref="L94:L95"/>
+    <mergeCell ref="M94:M95"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="K98:K99"/>
+    <mergeCell ref="L98:L99"/>
+    <mergeCell ref="M98:M99"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="K100:K101"/>
+    <mergeCell ref="L100:L101"/>
+    <mergeCell ref="M100:M101"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="L102:L103"/>
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="K105:M105"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="H36:H37"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="C42:C43"/>
@@ -9175,366 +9451,90 @@
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="H40:H41"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="J102:J103"/>
-    <mergeCell ref="K102:K103"/>
-    <mergeCell ref="L102:L103"/>
-    <mergeCell ref="M102:M103"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="K105:M105"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="J100:J101"/>
-    <mergeCell ref="K100:K101"/>
-    <mergeCell ref="L100:L101"/>
-    <mergeCell ref="M100:M101"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="H100:H101"/>
-    <mergeCell ref="J98:J99"/>
-    <mergeCell ref="K98:K99"/>
-    <mergeCell ref="L98:L99"/>
-    <mergeCell ref="M98:M99"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="H98:H99"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="H96:H97"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="J92:J93"/>
-    <mergeCell ref="K92:K93"/>
-    <mergeCell ref="L92:L93"/>
-    <mergeCell ref="M92:M93"/>
-    <mergeCell ref="J94:J95"/>
-    <mergeCell ref="K94:K95"/>
-    <mergeCell ref="L94:L95"/>
-    <mergeCell ref="M94:M95"/>
-    <mergeCell ref="J96:J97"/>
-    <mergeCell ref="K96:K97"/>
-    <mergeCell ref="L96:L97"/>
-    <mergeCell ref="M96:M97"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="K90:K91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="K86:K87"/>
-    <mergeCell ref="L86:L87"/>
-    <mergeCell ref="M86:M87"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="K88:K89"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="M88:M89"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="K84:K85"/>
-    <mergeCell ref="L84:L85"/>
-    <mergeCell ref="M84:M85"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="K76:K77"/>
-    <mergeCell ref="L76:L77"/>
-    <mergeCell ref="M76:M77"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="K78:K79"/>
-    <mergeCell ref="L78:L79"/>
-    <mergeCell ref="M78:M79"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="K80:K81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="K74:K75"/>
-    <mergeCell ref="L74:L75"/>
-    <mergeCell ref="M74:M75"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="K70:K71"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="K72:K73"/>
-    <mergeCell ref="L72:L73"/>
-    <mergeCell ref="M72:M73"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="K68:K69"/>
-    <mergeCell ref="L68:L69"/>
-    <mergeCell ref="M68:M69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="M66:M67"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="K66:K67"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="M64:M65"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="K60:K61"/>
+    <mergeCell ref="L60:L61"/>
+    <mergeCell ref="M60:M61"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="L46:L47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
